--- a/Historical Excel/Round 3/Trades Day 2 (Round 3).xlsx
+++ b/Historical Excel/Round 3/Trades Day 2 (Round 3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92c4f7ffed9c6980/Python/IntaraTradingAlgorithm/Historical Excel/Round 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{E0131669-CABC-4EAF-9170-350C219F8D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6FBE32C-DF6A-4C50-B5FC-410754971A1A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{E0131669-CABC-4EAF-9170-350C219F8D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A76529C-50FE-4BF2-8B88-5D4A4F52E5A4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{26B00CBD-22D1-4435-8D2F-21192D48D5C7}"/>
   </bookViews>
@@ -211,7 +211,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-AU" baseline="0"/>
-              <a:t> Pack</a:t>
+              <a:t> Pack Day 2</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -6649,13 +6649,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
+      <xdr:colOff>88899</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>98960</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
@@ -7075,7 +7075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398A2057-D3E7-460D-8DC7-D2D995F2787E}">
-  <dimension ref="A1:G1334"/>
+  <dimension ref="A1:K1334"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
@@ -14079,7 +14079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>982000</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>983700</v>
       </c>
@@ -14125,7 +14125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>984200</v>
       </c>
@@ -14148,7 +14148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>984700</v>
       </c>
@@ -14171,7 +14171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>992200</v>
       </c>
@@ -14194,7 +14194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>993200</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>994800</v>
       </c>
@@ -14240,7 +14240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>996500</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>900</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>2700</v>
       </c>
@@ -14308,8 +14308,12 @@
       <c r="G314">
         <v>8</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="K314">
+        <f>AVERAGE(F313:F789)</f>
+        <v>5257.6582809224319</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>2900</v>
       </c>
@@ -14332,7 +14336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>4800</v>
       </c>
@@ -14355,7 +14359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>5700</v>
       </c>
@@ -14378,7 +14382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>9900</v>
       </c>
@@ -14401,7 +14405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>10700</v>
       </c>
@@ -14424,7 +14428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>12100</v>
       </c>

--- a/Historical Excel/Round 3/Trades Day 2 (Round 3).xlsx
+++ b/Historical Excel/Round 3/Trades Day 2 (Round 3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92c4f7ffed9c6980/Python/IntaraTradingAlgorithm/Historical Excel/Round 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{E0131669-CABC-4EAF-9170-350C219F8D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A76529C-50FE-4BF2-8B88-5D4A4F52E5A4}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{E0131669-CABC-4EAF-9170-350C219F8D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E57B6373-BAB5-460F-9EFA-F86DAED93156}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{26B00CBD-22D1-4435-8D2F-21192D48D5C7}"/>
   </bookViews>
@@ -6648,16 +6648,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>88899</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>377535</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>13360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>98960</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>387596</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>175738</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6684,16 +6684,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>410882</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>24902</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>476855</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>165097</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>311020</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>376993</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>153396</xdr:rowOff>
+      <xdr:rowOff>112162</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7087,7 +7087,7 @@
     <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>10200</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>11200</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>15700</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>19100</v>
       </c>
@@ -7202,7 +7202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>29200</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>41100</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>44000</v>
       </c>
@@ -7270,8 +7270,12 @@
       <c r="G8">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I8">
+        <f>AVERAGE(F2:F312)</f>
+        <v>9986.6559485530543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>45100</v>
       </c>
@@ -7294,7 +7298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>49400</v>
       </c>
@@ -7317,7 +7321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>49800</v>
       </c>
@@ -7340,7 +7344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>58300</v>
       </c>
@@ -7363,7 +7367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>60700</v>
       </c>
@@ -7386,7 +7390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>70900</v>
       </c>
@@ -7409,7 +7413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>71800</v>
       </c>
@@ -7432,7 +7436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>72700</v>
       </c>
